--- a/week-02/Ex2A_events_normalized.xlsx
+++ b/week-02/Ex2A_events_normalized.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/ilee_my_yearupunited_org/Documents/Documents/DataAnalytics/week-02/"/>
@@ -15,11 +15,14 @@
   <sheets>
     <sheet name="events_sample" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="68" r:id="rId2"/>
+    <pivotCache cacheId="8" r:id="rId2"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -78,9 +81,51 @@
     <t>Event Name</t>
   </si>
   <si>
+    <t>Venue Location</t>
+  </si>
+  <si>
+    <t>Event Category</t>
+  </si>
+  <si>
+    <t>Category Code</t>
+  </si>
+  <si>
     <t>Event Date</t>
   </si>
   <si>
+    <t>Event Manager</t>
+  </si>
+  <si>
+    <t>Employee #</t>
+  </si>
+  <si>
+    <t>Mgr Email</t>
+  </si>
+  <si>
+    <t>Location Address</t>
+  </si>
+  <si>
+    <t>Location City</t>
+  </si>
+  <si>
+    <t>Location State</t>
+  </si>
+  <si>
+    <t>Location Zip</t>
+  </si>
+  <si>
+    <t>Venue ID</t>
+  </si>
+  <si>
+    <t>Venue Contact Name</t>
+  </si>
+  <si>
+    <t>Venue Email</t>
+  </si>
+  <si>
+    <t>Venue Phone</t>
+  </si>
+  <si>
     <t>Starlight Showcase</t>
   </si>
   <si>
@@ -93,6 +138,33 @@
     <t>Larry Song</t>
   </si>
   <si>
+    <t>u0156</t>
+  </si>
+  <si>
+    <t>larry.song@eventdoodle.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1847 Sunset Boulevard</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Los Angeles</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CA</t>
+  </si>
+  <si>
+    <t>Starlight_CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Maria Riley</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> maria.r@starlightbar.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (323) 555-0142</t>
+  </si>
+  <si>
     <t>Summer Jazz Festival</t>
   </si>
   <si>
@@ -102,6 +174,33 @@
     <t>Sarah Mitchell</t>
   </si>
   <si>
+    <t>u1023</t>
+  </si>
+  <si>
+    <t>sarah.mitchell@eventdoodle.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3250 Riverside Drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Austin</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TX</t>
+  </si>
+  <si>
+    <t>RivAmp_TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> James Mitchell</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jmitchell@riversideamp.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (512) 555-0298</t>
+  </si>
+  <si>
     <t>Comedy Night Live</t>
   </si>
   <si>
@@ -114,6 +213,30 @@
     <t>Mike Chen</t>
   </si>
   <si>
+    <t>u0561</t>
+  </si>
+  <si>
+    <t>mike.chen@eventdoodle.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 8001 Sunset Boulevard</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> West Hollywood</t>
+  </si>
+  <si>
+    <t>LafFctry_CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> David Chekov</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> david@laughfactory.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (323) 555-0187</t>
+  </si>
+  <si>
     <t>Tech Innovation Summit</t>
   </si>
   <si>
@@ -123,6 +246,27 @@
     <t>Conference</t>
   </si>
   <si>
+    <t xml:space="preserve"> 1201 Convention Plaza</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chicago</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> IL</t>
+  </si>
+  <si>
+    <t>DtwnCon_IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Patricia Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> p.anderson@dccchicago.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (312) 555-0456</t>
+  </si>
+  <si>
     <t>Sunset Poetry Reading</t>
   </si>
   <si>
@@ -135,6 +279,33 @@
     <t>Elena Rodriguez</t>
   </si>
   <si>
+    <t>u0865</t>
+  </si>
+  <si>
+    <t>elena.rodriguez@eventdoodle.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 428 Greenwich Avenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> New York</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NY</t>
+  </si>
+  <si>
+    <t>CafeB_NY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sophie Laurent</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> sophie@cafeboheme.nyc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (212) 555-0333</t>
+  </si>
+  <si>
     <t>Spring Food &amp; Wine Expo</t>
   </si>
   <si>
@@ -144,6 +315,12 @@
     <t>David Park</t>
   </si>
   <si>
+    <t>u0422</t>
+  </si>
+  <si>
+    <t>david.park@eventdoodle.com</t>
+  </si>
+  <si>
     <t>Indie Film Showcase</t>
   </si>
   <si>
@@ -153,6 +330,27 @@
     <t>Film</t>
   </si>
   <si>
+    <t xml:space="preserve"> 2847 Broadway Street</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Portland</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OR</t>
+  </si>
+  <si>
+    <t>MetroCin_OR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Robert Kim</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> robert.kim@metrocinema.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (503) 555-0721</t>
+  </si>
+  <si>
     <t>Corporate Leadership Forum</t>
   </si>
   <si>
@@ -162,6 +360,33 @@
     <t>Jennifer Wu</t>
   </si>
   <si>
+    <t>u0187</t>
+  </si>
+  <si>
+    <t>jennifer.wu@eventdoodle.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 500 Michigan Avenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Detroit</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MI</t>
+  </si>
+  <si>
+    <t>GrBall_MI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Elizabeth Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ethompson@grandballroom.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (313) 555-0892</t>
+  </si>
+  <si>
     <t>Blues &amp; BBQ Night</t>
   </si>
   <si>
@@ -171,6 +396,21 @@
     <t>Comedy Corner Club</t>
   </si>
   <si>
+    <t xml:space="preserve"> 156 Bleecker Street</t>
+  </si>
+  <si>
+    <t>ComCor_NY</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Michael O'Brien</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mike@comedycorner.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (212) 555-0654</t>
+  </si>
+  <si>
     <t>Art Walk Opening</t>
   </si>
   <si>
@@ -180,150 +420,6 @@
     <t>Art</t>
   </si>
   <si>
-    <t>larry.song@eventdoodle.com</t>
-  </si>
-  <si>
-    <t>sarah.mitchell@eventdoodle.com</t>
-  </si>
-  <si>
-    <t>mike.chen@eventdoodle.com</t>
-  </si>
-  <si>
-    <t>elena.rodriguez@eventdoodle.com</t>
-  </si>
-  <si>
-    <t>david.park@eventdoodle.com</t>
-  </si>
-  <si>
-    <t>jennifer.wu@eventdoodle.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1847 Sunset Boulevard</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Los Angeles</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> maria.r@starlightbar.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (323) 555-0142</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3250 Riverside Drive</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Austin</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TX</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> James Mitchell</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> jmitchell@riversideamp.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (512) 555-0298</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 8001 Sunset Boulevard</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> West Hollywood</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> david@laughfactory.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (323) 555-0187</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1201 Convention Plaza</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Chicago</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Patricia Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> p.anderson@dccchicago.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (312) 555-0456</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 428 Greenwich Avenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> New York</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NY</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sophie Laurent</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> sophie@cafeboheme.nyc</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (212) 555-0333</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2847 Broadway Street</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Portland</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Robert Kim</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> robert.kim@metrocinema.org</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (503) 555-0721</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 500 Michigan Avenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Detroit</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MI</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Elizabeth Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ethompson@grandballroom.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (313) 555-0892</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 156 Bleecker Street</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> mike@comedycorner.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (212) 555-0654</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 975 Art Walk Lane</t>
   </si>
   <si>
@@ -333,6 +429,9 @@
     <t xml:space="preserve"> FL</t>
   </si>
   <si>
+    <t>GallDst_FL</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Amanda Rivera</t>
   </si>
   <si>
@@ -342,177 +441,84 @@
     <t xml:space="preserve"> (305) 555-0401</t>
   </si>
   <si>
-    <t>Location Address</t>
-  </si>
-  <si>
-    <t>Location City</t>
-  </si>
-  <si>
-    <t>Location State</t>
-  </si>
-  <si>
-    <t>Location Zip</t>
-  </si>
-  <si>
-    <t>Venue Email</t>
-  </si>
-  <si>
-    <t>Venue Phone</t>
-  </si>
-  <si>
-    <t>Venue Contact Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Michael O'Brien</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Maria Riley</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> David Chekov</t>
-  </si>
-  <si>
     <t>1st table:</t>
   </si>
   <si>
+    <t xml:space="preserve">Venue </t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
     <t>2nd table:</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
+  </si>
+  <si>
+    <t>102 Total</t>
+  </si>
+  <si>
+    <t>103 Total</t>
+  </si>
+  <si>
+    <t>104 Total</t>
+  </si>
+  <si>
+    <t>105 Total</t>
+  </si>
+  <si>
+    <t>106 Total</t>
+  </si>
+  <si>
+    <t>107 Total</t>
+  </si>
+  <si>
+    <t>108 Total</t>
+  </si>
+  <si>
+    <t>109 Total</t>
+  </si>
+  <si>
+    <t>110 Total</t>
+  </si>
+  <si>
+    <t>111 Total</t>
+  </si>
+  <si>
+    <t>112 Total</t>
+  </si>
+  <si>
+    <t>Music Total</t>
+  </si>
+  <si>
+    <t>Comedy Total</t>
+  </si>
+  <si>
+    <t>Conference Total</t>
+  </si>
+  <si>
+    <t>Literary Total</t>
+  </si>
+  <si>
+    <t>Festival Total</t>
+  </si>
+  <si>
+    <t>Film Total</t>
+  </si>
+  <si>
+    <t>Art Total</t>
+  </si>
+  <si>
     <t>3rd table:</t>
   </si>
   <si>
-    <t>Event Category</t>
-  </si>
-  <si>
-    <t>Category Code</t>
-  </si>
-  <si>
-    <t>Event Manager</t>
-  </si>
-  <si>
-    <t>Mgr Email</t>
-  </si>
-  <si>
-    <t>Employee #</t>
-  </si>
-  <si>
-    <t>u0156</t>
-  </si>
-  <si>
-    <t>u1023</t>
-  </si>
-  <si>
-    <t>u0561</t>
-  </si>
-  <si>
-    <t>u0422</t>
-  </si>
-  <si>
-    <t>u0187</t>
-  </si>
-  <si>
-    <t>Venue Location</t>
-  </si>
-  <si>
-    <t>Venue ID</t>
-  </si>
-  <si>
-    <t>RivAmp_TX</t>
-  </si>
-  <si>
-    <t>Starlight_CA</t>
-  </si>
-  <si>
-    <t>LafFctry_CA</t>
-  </si>
-  <si>
-    <t>DtwnCon_IL</t>
-  </si>
-  <si>
-    <t>CafeB_NY</t>
-  </si>
-  <si>
-    <t>MetroCin_OR</t>
-  </si>
-  <si>
-    <t>GrBall_MI</t>
-  </si>
-  <si>
-    <t>ComCor_NY</t>
-  </si>
-  <si>
-    <t>GallDst_FL</t>
-  </si>
-  <si>
-    <t>u0865</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Column Labels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venue </t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>102 Total</t>
-  </si>
-  <si>
-    <t>103 Total</t>
-  </si>
-  <si>
-    <t>104 Total</t>
-  </si>
-  <si>
-    <t>105 Total</t>
-  </si>
-  <si>
-    <t>106 Total</t>
-  </si>
-  <si>
-    <t>107 Total</t>
-  </si>
-  <si>
-    <t>108 Total</t>
-  </si>
-  <si>
-    <t>109 Total</t>
-  </si>
-  <si>
-    <t>110 Total</t>
-  </si>
-  <si>
-    <t>111 Total</t>
-  </si>
-  <si>
-    <t>112 Total</t>
-  </si>
-  <si>
-    <t>Music Total</t>
-  </si>
-  <si>
-    <t>Comedy Total</t>
-  </si>
-  <si>
-    <t>Conference Total</t>
-  </si>
-  <si>
-    <t>Literary Total</t>
-  </si>
-  <si>
-    <t>Festival Total</t>
-  </si>
-  <si>
-    <t>Film Total</t>
-  </si>
-  <si>
-    <t>Art Total</t>
-  </si>
-  <si>
     <t>Location</t>
   </si>
   <si>
@@ -618,43 +624,43 @@
     <t>4th table:</t>
   </si>
   <si>
+    <t>Larry Song Total</t>
+  </si>
+  <si>
+    <t>Sarah Mitchell Total</t>
+  </si>
+  <si>
+    <t>Mike Chen Total</t>
+  </si>
+  <si>
+    <t>Elena Rodriguez Total</t>
+  </si>
+  <si>
+    <t>David Park Total</t>
+  </si>
+  <si>
+    <t>Jennifer Wu Total</t>
+  </si>
+  <si>
+    <t>u0156 Total</t>
+  </si>
+  <si>
+    <t>u1023 Total</t>
+  </si>
+  <si>
+    <t>u0561 Total</t>
+  </si>
+  <si>
+    <t>u0865 Total</t>
+  </si>
+  <si>
     <t>u0422 Total</t>
   </si>
   <si>
-    <t>u0865 Total</t>
-  </si>
-  <si>
     <t>u0187 Total</t>
   </si>
   <si>
-    <t>u0156 Total</t>
-  </si>
-  <si>
-    <t>u0561 Total</t>
-  </si>
-  <si>
-    <t>u1023 Total</t>
-  </si>
-  <si>
-    <t>Larry Song Total</t>
-  </si>
-  <si>
-    <t>Sarah Mitchell Total</t>
-  </si>
-  <si>
-    <t>Mike Chen Total</t>
-  </si>
-  <si>
-    <t>Elena Rodriguez Total</t>
-  </si>
-  <si>
-    <t>David Park Total</t>
-  </si>
-  <si>
-    <t>Jennifer Wu Total</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
+    <t>It was helpful to see that I have an understanding of the concept and it reassured me on that. However I was aware my formatting was off and it helped better assist with how to properly form them in a table. It gave some suggestions and feedback on changes I could make. The ones I utilized were to improve my underanding on how to properly group in the 1-3NF. I understand grouping data but can grow my understanding on creating a normalized relational table. I use Copilot to help me better understand how to form the tables and the new updated tables are as follows below.</t>
   </si>
   <si>
     <t>Events</t>
@@ -663,6 +669,24 @@
     <t>Venues</t>
   </si>
   <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Event Managers</t>
+  </si>
+  <si>
+    <t>PK: Event ID | FKs: Venue ID, Category Code, Employee #</t>
+  </si>
+  <si>
+    <t>PK: Venue ID; unique venue and location/contact details</t>
+  </si>
+  <si>
+    <t>PK: Category Code</t>
+  </si>
+  <si>
+    <t>PK: Employee #</t>
+  </si>
+  <si>
     <t>Venue Name</t>
   </si>
   <si>
@@ -687,190 +711,217 @@
     <t>Contact Phone</t>
   </si>
   <si>
-    <t>Categories</t>
-  </si>
-  <si>
     <t>Category Name</t>
   </si>
   <si>
-    <t>Event Managers</t>
-  </si>
-  <si>
     <t>Manager Name</t>
   </si>
   <si>
     <t>Manager Email</t>
   </si>
   <si>
+    <t>1847 Sunset Boulevard</t>
+  </si>
+  <si>
+    <t>Los Angeles</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Maria Riley</t>
+  </si>
+  <si>
+    <t>maria.r@starlightbar.com</t>
+  </si>
+  <si>
+    <t>(323) 555-0142</t>
+  </si>
+  <si>
+    <t>3250 Riverside Drive</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>James Mitchell</t>
+  </si>
+  <si>
+    <t>jmitchell@riversideamp.com</t>
+  </si>
+  <si>
+    <t>(512) 555-0298</t>
+  </si>
+  <si>
+    <t>8001 Sunset Boulevard</t>
+  </si>
+  <si>
+    <t>West Hollywood</t>
+  </si>
+  <si>
+    <t>David Chekov</t>
+  </si>
+  <si>
+    <t>david@laughfactory.com</t>
+  </si>
+  <si>
+    <t>(323) 555-0187</t>
+  </si>
+  <si>
+    <t>1201 Convention Plaza</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>Patricia Anderson</t>
+  </si>
+  <si>
+    <t>p.anderson@dccchicago.com</t>
+  </si>
+  <si>
+    <t>(312) 555-0456</t>
+  </si>
+  <si>
+    <t>428 Greenwich Avenue</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>Sophie Laurent</t>
+  </si>
+  <si>
+    <t>sophie@cafeboheme.nyc</t>
+  </si>
+  <si>
+    <t>(212) 555-0333</t>
+  </si>
+  <si>
+    <t>2847 Broadway Street</t>
+  </si>
+  <si>
+    <t>Portland</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>Robert Kim</t>
+  </si>
+  <si>
+    <t>robert.kim@metrocinema.org</t>
+  </si>
+  <si>
+    <t>(503) 555-0721</t>
+  </si>
+  <si>
+    <t>500 Michigan Avenue</t>
+  </si>
+  <si>
+    <t>Detroit</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>Elizabeth Thompson</t>
+  </si>
+  <si>
+    <t>ethompson@grandballroom.com</t>
+  </si>
+  <si>
+    <t>(313) 555-0892</t>
+  </si>
+  <si>
+    <t>156 Bleecker Street</t>
+  </si>
+  <si>
+    <t>Michael O'Brien</t>
+  </si>
+  <si>
+    <t>mike@comedycorner.com</t>
+  </si>
+  <si>
+    <t>(212) 555-0654</t>
+  </si>
+  <si>
+    <t>975 Art Walk Lane</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>Amanda Rivera</t>
+  </si>
+  <si>
+    <t>arivera@gallerydistrict.org</t>
+  </si>
+  <si>
+    <t>(305) 555-0401</t>
+  </si>
+  <si>
+    <t>Normalization and Relationships</t>
+  </si>
+  <si>
     <t>Form</t>
   </si>
   <si>
+    <t>Requirement met</t>
+  </si>
+  <si>
+    <t>Parent key</t>
+  </si>
+  <si>
+    <t>Foreign key</t>
+  </si>
+  <si>
+    <t>Relationship</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
     <t>1NF</t>
   </si>
   <si>
+    <t>Atomic values; one record per row</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>No repeating groups</t>
+  </si>
+  <si>
+    <t>Met</t>
+  </si>
+  <si>
     <t>2NF</t>
   </si>
   <si>
+    <t>All attributes depend on the whole primary key</t>
+  </si>
+  <si>
+    <t>Single-column PKs</t>
+  </si>
+  <si>
     <t>3NF</t>
   </si>
   <si>
-    <t>1847 Sunset Boulevard</t>
-  </si>
-  <si>
-    <t>Los Angeles</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>Maria Riley</t>
-  </si>
-  <si>
-    <t>maria.r@starlightbar.com</t>
-  </si>
-  <si>
-    <t>(323) 555-0142</t>
-  </si>
-  <si>
-    <t>3250 Riverside Drive</t>
-  </si>
-  <si>
-    <t>Austin</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>James Mitchell</t>
-  </si>
-  <si>
-    <t>jmitchell@riversideamp.com</t>
-  </si>
-  <si>
-    <t>(512) 555-0298</t>
-  </si>
-  <si>
-    <t>8001 Sunset Boulevard</t>
-  </si>
-  <si>
-    <t>West Hollywood</t>
-  </si>
-  <si>
-    <t>David Chekov</t>
-  </si>
-  <si>
-    <t>david@laughfactory.com</t>
-  </si>
-  <si>
-    <t>(323) 555-0187</t>
-  </si>
-  <si>
-    <t>1201 Convention Plaza</t>
-  </si>
-  <si>
-    <t>Chicago</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>Patricia Anderson</t>
-  </si>
-  <si>
-    <t>p.anderson@dccchicago.com</t>
-  </si>
-  <si>
-    <t>(312) 555-0456</t>
-  </si>
-  <si>
-    <t>428 Greenwich Avenue</t>
-  </si>
-  <si>
-    <t>New York</t>
-  </si>
-  <si>
-    <t>NY</t>
-  </si>
-  <si>
-    <t>Sophie Laurent</t>
-  </si>
-  <si>
-    <t>sophie@cafeboheme.nyc</t>
-  </si>
-  <si>
-    <t>(212) 555-0333</t>
-  </si>
-  <si>
-    <t>2847 Broadway Street</t>
-  </si>
-  <si>
-    <t>Portland</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>Robert Kim</t>
-  </si>
-  <si>
-    <t>robert.kim@metrocinema.org</t>
-  </si>
-  <si>
-    <t>(503) 555-0721</t>
-  </si>
-  <si>
-    <t>500 Michigan Avenue</t>
-  </si>
-  <si>
-    <t>Detroit</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>Elizabeth Thompson</t>
-  </si>
-  <si>
-    <t>ethompson@grandballroom.com</t>
-  </si>
-  <si>
-    <t>(313) 555-0892</t>
-  </si>
-  <si>
-    <t>156 Bleecker Street</t>
-  </si>
-  <si>
-    <t>Michael O'Brien</t>
-  </si>
-  <si>
-    <t>mike@comedycorner.com</t>
-  </si>
-  <si>
-    <t>(212) 555-0654</t>
-  </si>
-  <si>
-    <t>975 Art Walk Lane</t>
-  </si>
-  <si>
-    <t>Miami</t>
-  </si>
-  <si>
-    <t>FL</t>
-  </si>
-  <si>
-    <t>Amanda Rivera</t>
-  </si>
-  <si>
-    <t>arivera@gallerydistrict.org</t>
-  </si>
-  <si>
-    <t>(305) 555-0401</t>
-  </si>
-  <si>
-    <t>Parent key</t>
-  </si>
-  <si>
-    <t>Relationship</t>
+    <t>No transitive dependencies</t>
   </si>
   <si>
     <t>tblVenues[Venue ID]</t>
@@ -879,6 +930,9 @@
     <t>tblEvents[Venue ID]</t>
   </si>
   <si>
+    <t>One-to-many</t>
+  </si>
+  <si>
     <t>tblCategories[Category Code]</t>
   </si>
   <si>
@@ -889,57 +943,6 @@
   </si>
   <si>
     <t>tblEvents[Employee #]</t>
-  </si>
-  <si>
-    <t>PK: Event ID | FKs: Venue ID, Category Code, Employee #</t>
-  </si>
-  <si>
-    <t>PK: Venue ID; unique venue and location/contact details</t>
-  </si>
-  <si>
-    <t>PK: Category Code</t>
-  </si>
-  <si>
-    <t>PK: Employee #</t>
-  </si>
-  <si>
-    <t>Normalization and Relationships</t>
-  </si>
-  <si>
-    <t>Requirement met</t>
-  </si>
-  <si>
-    <t>Foreign key</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Atomic values; one record per row</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>No repeating groups</t>
-  </si>
-  <si>
-    <t>Met</t>
-  </si>
-  <si>
-    <t>All attributes depend on the whole primary key</t>
-  </si>
-  <si>
-    <t>Single-column PKs</t>
-  </si>
-  <si>
-    <t>No transitive dependencies</t>
-  </si>
-  <si>
-    <t>One-to-many</t>
-  </si>
-  <si>
-    <t>It was helpful to see that I have an understanding of the concept and it reassured me on that. However I was aware my formatting was off and it helped better assist with how to properly form them in a table. It gave some suggestions and feedback on changes I could make. The ones I utilized were to improve my underanding on how to properly group in the 1-3NF. I understand grouping data but can grow my understanding on creating a normalized relational table. I use Copilot to help me better understand how to form the tables and the new updated tables are as follows below.</t>
   </si>
 </sst>
 </file>
@@ -947,9 +950,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="00000"/>
+    <numFmt numFmtId="164" formatCode="00000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1503,7 +1506,6 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1513,19 +1515,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1573,12 +1576,6 @@
   </cellStyles>
   <dxfs count="6">
     <dxf>
-      <numFmt numFmtId="168" formatCode="00000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <color rgb="FFFFFFFF"/>
@@ -1603,6 +1600,9 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="00000"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FFFFFFFF"/>
@@ -1613,6 +1613,9 @@
           <bgColor rgb="FF5B9BD5"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -1637,10 +1640,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2250,6 +2249,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -2469,619 +2471,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9BB63B2-413A-4A6A-8B42-79A2A3CC9817}" name="PivotTable18" cacheId="68" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B49:AI52" firstHeaderRow="1" firstDataRow="4" firstDataCol="0"/>
-  <pivotFields count="19">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="8">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="8">
-        <item x="6"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="9"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="369">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item x="162"/>
-        <item x="163"/>
-        <item x="164"/>
-        <item x="165"/>
-        <item x="166"/>
-        <item x="167"/>
-        <item x="168"/>
-        <item x="169"/>
-        <item x="170"/>
-        <item x="171"/>
-        <item x="172"/>
-        <item x="173"/>
-        <item x="174"/>
-        <item x="175"/>
-        <item x="176"/>
-        <item x="177"/>
-        <item x="178"/>
-        <item x="179"/>
-        <item x="180"/>
-        <item x="181"/>
-        <item x="182"/>
-        <item x="183"/>
-        <item x="184"/>
-        <item x="185"/>
-        <item x="186"/>
-        <item x="187"/>
-        <item x="188"/>
-        <item x="189"/>
-        <item x="190"/>
-        <item x="191"/>
-        <item x="192"/>
-        <item x="193"/>
-        <item x="194"/>
-        <item x="195"/>
-        <item x="196"/>
-        <item x="197"/>
-        <item x="198"/>
-        <item x="199"/>
-        <item x="200"/>
-        <item x="201"/>
-        <item x="202"/>
-        <item x="203"/>
-        <item x="204"/>
-        <item x="205"/>
-        <item x="206"/>
-        <item x="207"/>
-        <item x="208"/>
-        <item x="209"/>
-        <item x="210"/>
-        <item x="211"/>
-        <item x="212"/>
-        <item x="213"/>
-        <item x="214"/>
-        <item x="215"/>
-        <item x="216"/>
-        <item x="217"/>
-        <item x="218"/>
-        <item x="219"/>
-        <item x="220"/>
-        <item x="221"/>
-        <item x="222"/>
-        <item x="223"/>
-        <item x="224"/>
-        <item x="225"/>
-        <item x="226"/>
-        <item x="227"/>
-        <item x="228"/>
-        <item x="229"/>
-        <item x="230"/>
-        <item x="231"/>
-        <item x="232"/>
-        <item x="233"/>
-        <item x="234"/>
-        <item x="235"/>
-        <item x="236"/>
-        <item x="237"/>
-        <item x="238"/>
-        <item x="239"/>
-        <item x="240"/>
-        <item x="241"/>
-        <item x="242"/>
-        <item x="243"/>
-        <item x="244"/>
-        <item x="245"/>
-        <item x="246"/>
-        <item x="247"/>
-        <item x="248"/>
-        <item x="249"/>
-        <item x="250"/>
-        <item x="251"/>
-        <item x="252"/>
-        <item x="253"/>
-        <item x="254"/>
-        <item x="255"/>
-        <item x="256"/>
-        <item x="257"/>
-        <item x="258"/>
-        <item x="259"/>
-        <item x="260"/>
-        <item x="261"/>
-        <item x="262"/>
-        <item x="263"/>
-        <item x="264"/>
-        <item x="265"/>
-        <item x="266"/>
-        <item x="267"/>
-        <item x="268"/>
-        <item x="269"/>
-        <item x="270"/>
-        <item x="271"/>
-        <item x="272"/>
-        <item x="273"/>
-        <item x="274"/>
-        <item x="275"/>
-        <item x="276"/>
-        <item x="277"/>
-        <item x="278"/>
-        <item x="279"/>
-        <item x="280"/>
-        <item x="281"/>
-        <item x="282"/>
-        <item x="283"/>
-        <item x="284"/>
-        <item x="285"/>
-        <item x="286"/>
-        <item x="287"/>
-        <item x="288"/>
-        <item x="289"/>
-        <item x="290"/>
-        <item x="291"/>
-        <item x="292"/>
-        <item x="293"/>
-        <item x="294"/>
-        <item x="295"/>
-        <item x="296"/>
-        <item x="297"/>
-        <item x="298"/>
-        <item x="299"/>
-        <item x="300"/>
-        <item x="301"/>
-        <item x="302"/>
-        <item x="303"/>
-        <item x="304"/>
-        <item x="305"/>
-        <item x="306"/>
-        <item x="307"/>
-        <item x="308"/>
-        <item x="309"/>
-        <item x="310"/>
-        <item x="311"/>
-        <item x="312"/>
-        <item x="313"/>
-        <item x="314"/>
-        <item x="315"/>
-        <item x="316"/>
-        <item x="317"/>
-        <item x="318"/>
-        <item x="319"/>
-        <item x="320"/>
-        <item x="321"/>
-        <item x="322"/>
-        <item x="323"/>
-        <item x="324"/>
-        <item x="325"/>
-        <item x="326"/>
-        <item x="327"/>
-        <item x="328"/>
-        <item x="329"/>
-        <item x="330"/>
-        <item x="331"/>
-        <item x="332"/>
-        <item x="333"/>
-        <item x="334"/>
-        <item x="335"/>
-        <item x="336"/>
-        <item x="337"/>
-        <item x="338"/>
-        <item x="339"/>
-        <item x="340"/>
-        <item x="341"/>
-        <item x="342"/>
-        <item x="343"/>
-        <item x="344"/>
-        <item x="345"/>
-        <item x="346"/>
-        <item x="347"/>
-        <item x="348"/>
-        <item x="349"/>
-        <item x="350"/>
-        <item x="351"/>
-        <item x="352"/>
-        <item x="353"/>
-        <item x="354"/>
-        <item x="355"/>
-        <item x="356"/>
-        <item x="357"/>
-        <item x="358"/>
-        <item x="359"/>
-        <item x="360"/>
-        <item x="361"/>
-        <item x="362"/>
-        <item x="363"/>
-        <item x="364"/>
-        <item x="365"/>
-        <item x="366"/>
-        <item x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colFields count="3">
-    <field x="0"/>
-    <field x="3"/>
-    <field x="4"/>
-  </colFields>
-  <colItems count="34">
-    <i>
-      <x/>
-      <x v="6"/>
-      <x v="6"/>
-    </i>
-    <i t="default" r="1">
-      <x v="6"/>
-    </i>
-    <i t="default">
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-      <x v="6"/>
-      <x v="6"/>
-    </i>
-    <i t="default" r="1">
-      <x v="6"/>
-    </i>
-    <i t="default">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x v="1"/>
-      <x v="1"/>
-    </i>
-    <i t="default" r="1">
-      <x v="1"/>
-    </i>
-    <i t="default">
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-      <x v="2"/>
-      <x v="2"/>
-    </i>
-    <i t="default" r="1">
-      <x v="2"/>
-    </i>
-    <i t="default">
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-      <x v="5"/>
-      <x v="5"/>
-    </i>
-    <i t="default" r="1">
-      <x v="5"/>
-    </i>
-    <i t="default">
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-      <x v="3"/>
-      <x v="3"/>
-    </i>
-    <i t="default" r="1">
-      <x v="3"/>
-    </i>
-    <i t="default">
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-      <x v="4"/>
-      <x v="4"/>
-    </i>
-    <i t="default" r="1">
-      <x v="4"/>
-    </i>
-    <i t="default">
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-      <x v="2"/>
-      <x v="2"/>
-    </i>
-    <i t="default" r="1">
-      <x v="2"/>
-    </i>
-    <i t="default">
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-      <x v="6"/>
-      <x v="6"/>
-    </i>
-    <i t="default" r="1">
-      <x v="6"/>
-    </i>
-    <i t="default">
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-      <x v="1"/>
-      <x v="1"/>
-    </i>
-    <i t="default" r="1">
-      <x v="1"/>
-    </i>
-    <i t="default">
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-      <x/>
-      <x/>
-    </i>
-    <i t="default" r="1">
-      <x/>
-    </i>
-    <i t="default">
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D9E9415-E1E0-4951-A0F6-37B0F57FC795}" name="PivotTable17" cacheId="68" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2D9E9415-E1E0-4951-A0F6-37B0F57FC795}" name="PivotTable17" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B17:B45" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -3281,8 +2671,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC344B1F-3FA0-4271-AAEE-80D1E6EFF8A5}" name="PivotTable16" cacheId="68" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DC344B1F-3FA0-4271-AAEE-80D1E6EFF8A5}" name="PivotTable16" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B73:AT77" firstHeaderRow="1" firstDataRow="5" firstDataCol="0"/>
   <pivotFields count="19">
     <pivotField axis="axisCol" showAll="0">
@@ -3946,8 +3336,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{261C357F-6D96-490F-88B9-F03995C68D26}" name="PivotTable14" cacheId="68" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{261C357F-6D96-490F-88B9-F03995C68D26}" name="PivotTable14" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B56:AS61" firstHeaderRow="1" firstDataRow="6" firstDataCol="0"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -4627,13 +4017,625 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9BB63B2-413A-4A6A-8B42-79A2A3CC9817}" name="PivotTable18" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B49:AI52" firstHeaderRow="1" firstDataRow="4" firstDataCol="0"/>
+  <pivotFields count="19">
+    <pivotField axis="axisCol" showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="8">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="8">
+        <item x="6"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="369">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item x="364"/>
+        <item x="365"/>
+        <item x="366"/>
+        <item x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="3">
+    <field x="0"/>
+    <field x="3"/>
+    <field x="4"/>
+  </colFields>
+  <colItems count="34">
+    <i>
+      <x/>
+      <x v="6"/>
+      <x v="6"/>
+    </i>
+    <i t="default" r="1">
+      <x v="6"/>
+    </i>
+    <i t="default">
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x v="6"/>
+      <x v="6"/>
+    </i>
+    <i t="default" r="1">
+      <x v="6"/>
+    </i>
+    <i t="default">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="1"/>
+      <x v="1"/>
+    </i>
+    <i t="default" r="1">
+      <x v="1"/>
+    </i>
+    <i t="default">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x v="2"/>
+      <x v="2"/>
+    </i>
+    <i t="default" r="1">
+      <x v="2"/>
+    </i>
+    <i t="default">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+      <x v="5"/>
+      <x v="5"/>
+    </i>
+    <i t="default" r="1">
+      <x v="5"/>
+    </i>
+    <i t="default">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+      <x v="3"/>
+      <x v="3"/>
+    </i>
+    <i t="default" r="1">
+      <x v="3"/>
+    </i>
+    <i t="default">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+      <x v="4"/>
+      <x v="4"/>
+    </i>
+    <i t="default" r="1">
+      <x v="4"/>
+    </i>
+    <i t="default">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+      <x v="2"/>
+      <x v="2"/>
+    </i>
+    <i t="default" r="1">
+      <x v="2"/>
+    </i>
+    <i t="default">
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+      <x v="6"/>
+      <x v="6"/>
+    </i>
+    <i t="default" r="1">
+      <x v="6"/>
+    </i>
+    <i t="default">
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+      <x v="1"/>
+      <x v="1"/>
+    </i>
+    <i t="default" r="1">
+      <x v="1"/>
+    </i>
+    <i t="default">
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+      <x/>
+      <x/>
+    </i>
+    <i t="default" r="1">
+      <x/>
+    </i>
+    <i t="default">
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F1390616-5330-405B-9DBB-709C5BC4D691}" name="tblEvents" displayName="tblEvents" ref="A99:F110" totalsRowShown="0">
   <autoFilter ref="A99:F110" xr:uid="{F1390616-5330-405B-9DBB-709C5BC4D691}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{420D12AA-1EE8-42CA-B81E-0A9FE0F4A0CA}" name="Event ID" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{4ECAF7FB-6D61-40C8-870D-8EE379EEBFDA}" name="Event Name"/>
-    <tableColumn id="3" xr3:uid="{82F0FDA5-564E-4FAE-9092-65EF10976CDC}" name="Event Date" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{82F0FDA5-564E-4FAE-9092-65EF10976CDC}" name="Event Date" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{66E833B3-3FEB-4B66-BB05-2651F5300EDC}" name="Venue ID"/>
     <tableColumn id="5" xr3:uid="{67237E46-1798-496D-930A-1FCFE219CFCF}" name="Category Code"/>
     <tableColumn id="6" xr3:uid="{10CB65DC-2AD0-489B-9452-37F31573FC6B}" name="Employee #"/>
@@ -4646,12 +4648,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6AB560E8-CA59-4700-87F5-3EA16D5B1BFC}" name="tblVenues" displayName="tblVenues" ref="H99:P108" totalsRowShown="0">
   <autoFilter ref="H99:P108" xr:uid="{6AB560E8-CA59-4700-87F5-3EA16D5B1BFC}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{3A54B943-EAFA-4A72-A181-6051051CEF0E}" name="Venue ID" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{3A54B943-EAFA-4A72-A181-6051051CEF0E}" name="Venue ID" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{1108C831-7211-4D92-BF2E-629714153CA2}" name="Venue Name"/>
     <tableColumn id="3" xr3:uid="{1AAF0FFC-B953-4960-9287-9E62725FA1B7}" name="Address"/>
     <tableColumn id="4" xr3:uid="{5FF15322-1282-4B72-99D2-DD64A950268B}" name="City"/>
     <tableColumn id="5" xr3:uid="{73E14D4E-91E9-4355-801F-DA0A9C019261}" name="State"/>
-    <tableColumn id="6" xr3:uid="{465AF727-1ED3-4DD8-A24A-A7E0FEDC2D7B}" name="ZIP Code" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{465AF727-1ED3-4DD8-A24A-A7E0FEDC2D7B}" name="ZIP Code" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{BF3E1B91-9D60-4453-80E0-5F3A1933E25B}" name="Contact Name"/>
     <tableColumn id="8" xr3:uid="{3A46F687-BF1D-42B4-AAB3-626EDC9A27F7}" name="Contact Email"/>
     <tableColumn id="9" xr3:uid="{516AF048-FFD5-4AB0-A111-FB828F2AD58E}" name="Contact Phone"/>
@@ -4664,7 +4666,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{BD68B120-785E-4D8C-B2D9-40221781D509}" name="tblCategories" displayName="tblCategories" ref="R99:S106" totalsRowShown="0">
   <autoFilter ref="R99:S106" xr:uid="{BD68B120-785E-4D8C-B2D9-40221781D509}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{AF6B941E-9569-4CD0-AC52-62E9B0F66F75}" name="Category Code" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{AF6B941E-9569-4CD0-AC52-62E9B0F66F75}" name="Category Code" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{7FC5FD1B-09B2-481E-ABE7-24B9C931E12D}" name="Category Name"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -4675,7 +4677,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{04741E1D-316D-4AC3-A41B-2A9FAC119B87}" name="tblManagers" displayName="tblManagers" ref="U99:W105" totalsRowShown="0">
   <autoFilter ref="U99:W105" xr:uid="{04741E1D-316D-4AC3-A41B-2A9FAC119B87}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3DA783C1-5137-433C-9463-D7F3D930B4FB}" name="Employee #" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{3DA783C1-5137-433C-9463-D7F3D930B4FB}" name="Employee #" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{838AC6C2-6FF9-4718-B21D-7B0E25FD5B89}" name="Manager Name"/>
     <tableColumn id="3" xr3:uid="{5CC14D44-3080-4224-9B45-0DDE11E6722B}" name="Manager Email"/>
   </tableColumns>
@@ -5001,87 +5003,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA38BEC-78EC-44DC-83F3-AA711D021920}">
   <dimension ref="A1:AT119"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
-    <col min="2" max="2" width="30.5546875" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="6" width="18.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" customWidth="1"/>
-    <col min="9" max="9" width="28.6640625" customWidth="1"/>
-    <col min="10" max="10" width="32.44140625" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" customWidth="1"/>
-    <col min="12" max="12" width="10.21875" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" customWidth="1"/>
-    <col min="14" max="14" width="23.109375" customWidth="1"/>
-    <col min="15" max="15" width="34.21875" customWidth="1"/>
-    <col min="16" max="16" width="20.33203125" customWidth="1"/>
-    <col min="17" max="17" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="19.44140625" customWidth="1"/>
-    <col min="20" max="20" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" customWidth="1"/>
+    <col min="4" max="6" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" customWidth="1"/>
+    <col min="10" max="10" width="32.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="23.140625" customWidth="1"/>
+    <col min="15" max="15" width="34.28515625" customWidth="1"/>
+    <col min="16" max="16" width="20.28515625" customWidth="1"/>
+    <col min="17" max="17" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="19.42578125" customWidth="1"/>
+    <col min="20" max="20" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.7109375" customWidth="1"/>
     <col min="22" max="22" width="25" customWidth="1"/>
     <col min="23" max="23" width="38" customWidth="1"/>
-    <col min="24" max="24" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="15" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="11" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="30.5546875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="75" max="75" width="11" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5089,63 +5091,63 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>107</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>7</v>
@@ -5154,51 +5156,51 @@
         <v>46095</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M2">
         <v>90026</v>
       </c>
       <c r="N2" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="P2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>103</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -5207,51 +5209,51 @@
         <v>46194</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="I3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" t="s">
         <v>37</v>
-      </c>
-      <c r="J3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L3" t="s">
-        <v>49</v>
       </c>
       <c r="M3">
         <v>78741</v>
       </c>
       <c r="N3" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="O3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="P3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -5260,51 +5262,51 @@
         <v>46115</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M4">
         <v>90046</v>
       </c>
       <c r="N4" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="O4" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="P4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Q4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5313,13 +5315,13 @@
         <v>46157</v>
       </c>
       <c r="G5" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
         <v>57</v>
@@ -5334,30 +5336,30 @@
         <v>60616</v>
       </c>
       <c r="N5" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="O5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -5366,51 +5368,51 @@
         <v>46109</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="J6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="M6">
         <v>10011</v>
       </c>
       <c r="N6" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="O6" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="P6" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="Q6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>107</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -5419,13 +5421,13 @@
         <v>46130</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="J7" t="s">
         <v>57</v>
@@ -5440,30 +5442,30 @@
         <v>60616</v>
       </c>
       <c r="N7" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="O7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -5472,51 +5474,51 @@
         <v>46144</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J8" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="K8" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="L8" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="M8">
         <v>97214</v>
       </c>
       <c r="N8" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="O8" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="P8" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="Q8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>109</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -5525,51 +5527,51 @@
         <v>46181</v>
       </c>
       <c r="G9" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="H9" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="I9" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="J9" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="K9" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="L9" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="M9">
         <v>48226</v>
       </c>
       <c r="N9" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="O9" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="Q9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -5578,51 +5580,51 @@
         <v>46215</v>
       </c>
       <c r="G10" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J10" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M10">
         <v>90026</v>
       </c>
       <c r="N10" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="P10" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -5631,51 +5633,51 @@
         <v>46102</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J11" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="K11" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="L11" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="M11">
         <v>10012</v>
       </c>
       <c r="N11" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="O11" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="P11" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="Q11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>112</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5684,210 +5686,210 @@
         <v>46137</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="H12" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="I12" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="J12" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="K12" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="L12" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="M12">
         <v>33132</v>
       </c>
       <c r="N12" t="s">
+        <v>118</v>
+      </c>
+      <c r="O12" t="s">
+        <v>119</v>
+      </c>
+      <c r="P12" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="2" customFormat="1" ht="15" thickBot="1"/>
+    <row r="15" spans="1:17" ht="15" thickTop="1"/>
+    <row r="16" spans="1:17">
+      <c r="A16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="O12" t="s">
-        <v>87</v>
-      </c>
-      <c r="P12" t="s">
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="B33" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="B34" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="B35" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="B36" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="Q12" t="s">
+    </row>
+    <row r="37" spans="1:2">
+      <c r="B37" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:17" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="38" spans="1:2">
+      <c r="B38" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="B39" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="B40" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="B41" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="B42" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="B43" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="B44" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="B45" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B22" s="8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B23" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B25" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B26" s="9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B27" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B28" s="8" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B29" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B30" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B31" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B32" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B33" s="7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B34" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B35" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B36" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B37" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B38" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B39" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B40" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B41" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B42" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B43" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B44" s="9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B45" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B48" s="3" t="s">
+    <row r="49" spans="1:45">
+      <c r="B49" s="5" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="49" spans="1:45" x14ac:dyDescent="0.3">
-      <c r="B49" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
     </row>
-    <row r="50" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:45">
       <c r="B50">
         <v>102</v>
       </c>
@@ -5958,75 +5960,75 @@
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:45">
       <c r="B51" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C51" t="s">
         <v>140</v>
       </c>
       <c r="E51" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
         <v>140</v>
       </c>
       <c r="H51" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="I51" t="s">
         <v>141</v>
       </c>
       <c r="K51" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="L51" t="s">
         <v>142</v>
       </c>
       <c r="N51" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="O51" t="s">
         <v>143</v>
       </c>
       <c r="Q51" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="R51" t="s">
         <v>144</v>
       </c>
       <c r="T51" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="U51" t="s">
         <v>145</v>
       </c>
       <c r="W51" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="X51" t="s">
         <v>142</v>
       </c>
       <c r="Z51" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="AA51" t="s">
         <v>140</v>
       </c>
       <c r="AC51" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="AD51" t="s">
         <v>141</v>
       </c>
       <c r="AF51" t="s">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="AG51" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:45">
       <c r="B52">
         <v>7</v>
       </c>
@@ -6061,277 +6063,277 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:45">
       <c r="A55" s="4" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="56" spans="1:45" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="56" spans="1:45">
       <c r="B56" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="57" spans="1:45" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:45">
       <c r="B57" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F57" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G57" t="s">
         <v>58</v>
       </c>
       <c r="K57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="P57" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q57" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="U57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V57" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="Z57" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA57" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="AH57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AI57" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="AM57" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN57" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AR57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AS57" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="58" spans="1:45" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:45">
       <c r="B58" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E58" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G58" t="s">
         <v>59</v>
       </c>
       <c r="J58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L58" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="O58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q58" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="T58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="V58" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="Y58" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG58" t="s">
+        <v>162</v>
+      </c>
+      <c r="AI58" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>163</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>25</v>
+      </c>
+      <c r="AQ58" t="s">
         <v>160</v>
       </c>
-      <c r="AA58" t="s">
-        <v>65</v>
-      </c>
-      <c r="AG58" t="s">
-        <v>161</v>
-      </c>
-      <c r="AI58" t="s">
-        <v>71</v>
-      </c>
-      <c r="AL58" t="s">
-        <v>162</v>
-      </c>
-      <c r="AN58" t="s">
-        <v>44</v>
-      </c>
-      <c r="AQ58" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="59" spans="1:45" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:45">
       <c r="B59" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D59" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G59" t="s">
         <v>57</v>
       </c>
       <c r="I59" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L59" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="N59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q59" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="S59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="V59" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="X59" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA59" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="AC59" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AD59" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="AF59" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AI59" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="AK59" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AN59" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="AP59" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="60" spans="1:45" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:45">
       <c r="B60">
         <v>78741</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G60">
         <v>60616</v>
       </c>
       <c r="H60" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L60">
         <v>48226</v>
       </c>
       <c r="M60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q60">
         <v>90026</v>
       </c>
       <c r="R60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V60">
         <v>33132</v>
       </c>
       <c r="W60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA60">
         <v>10012</v>
       </c>
       <c r="AB60" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD60">
         <v>10011</v>
       </c>
       <c r="AE60" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AI60">
         <v>97214</v>
       </c>
       <c r="AJ60" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AN60">
         <v>90046</v>
       </c>
       <c r="AO60" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="61" spans="1:45" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="61" spans="1:45">
       <c r="B61" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="G61" t="s">
+        <v>60</v>
+      </c>
+      <c r="L61" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>26</v>
+      </c>
+      <c r="V61" t="s">
         <v>118</v>
       </c>
-      <c r="L61" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>116</v>
-      </c>
-      <c r="V61" t="s">
-        <v>123</v>
-      </c>
       <c r="AA61" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="AD61" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="AI61" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="AN61" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="72" spans="1:46" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" spans="1:46">
       <c r="A72" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="73" spans="1:46" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:46">
       <c r="B73" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="74" spans="1:46" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:46">
       <c r="B74">
         <v>102</v>
       </c>
@@ -6402,998 +6404,998 @@
         <v>125</v>
       </c>
     </row>
-    <row r="75" spans="1:46" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:46">
       <c r="B75" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D75" t="s">
+        <v>183</v>
+      </c>
+      <c r="F75" t="s">
+        <v>32</v>
+      </c>
+      <c r="H75" t="s">
+        <v>184</v>
+      </c>
+      <c r="J75" t="s">
+        <v>45</v>
+      </c>
+      <c r="L75" t="s">
+        <v>185</v>
+      </c>
+      <c r="N75" t="s">
+        <v>32</v>
+      </c>
+      <c r="P75" t="s">
+        <v>184</v>
+      </c>
+      <c r="R75" t="s">
+        <v>67</v>
+      </c>
+      <c r="T75" t="s">
+        <v>186</v>
+      </c>
+      <c r="V75" t="s">
+        <v>79</v>
+      </c>
+      <c r="X75" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB75" t="s">
+        <v>185</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF75" t="s">
         <v>188</v>
       </c>
-      <c r="F75" t="s">
-        <v>9</v>
-      </c>
-      <c r="H75" t="s">
+      <c r="AH75" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ75" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>185</v>
+      </c>
+      <c r="AP75" t="s">
+        <v>67</v>
+      </c>
+      <c r="AR75" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:46">
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" t="s">
         <v>189</v>
       </c>
-      <c r="J75" t="s">
-        <v>13</v>
-      </c>
-      <c r="L75" t="s">
+      <c r="F76" t="s">
+        <v>33</v>
+      </c>
+      <c r="G76" t="s">
         <v>190</v>
       </c>
-      <c r="N75" t="s">
-        <v>9</v>
-      </c>
-      <c r="P75" t="s">
-        <v>189</v>
-      </c>
-      <c r="R75" t="s">
-        <v>20</v>
-      </c>
-      <c r="T75" t="s">
+      <c r="J76" t="s">
+        <v>46</v>
+      </c>
+      <c r="K76" t="s">
         <v>191</v>
       </c>
-      <c r="V75" t="s">
-        <v>23</v>
-      </c>
-      <c r="X75" t="s">
+      <c r="N76" t="s">
+        <v>33</v>
+      </c>
+      <c r="O76" t="s">
+        <v>190</v>
+      </c>
+      <c r="R76" t="s">
+        <v>68</v>
+      </c>
+      <c r="S76" t="s">
         <v>192</v>
       </c>
-      <c r="Z75" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB75" t="s">
+      <c r="V76" t="s">
+        <v>80</v>
+      </c>
+      <c r="W76" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>191</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>194</v>
+      </c>
+      <c r="AH76" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI76" t="s">
         <v>190</v>
       </c>
-      <c r="AD75" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF75" t="s">
-        <v>193</v>
-      </c>
-      <c r="AH75" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ75" t="s">
-        <v>189</v>
-      </c>
-      <c r="AL75" t="s">
-        <v>13</v>
-      </c>
-      <c r="AN75" t="s">
-        <v>190</v>
-      </c>
-      <c r="AP75" t="s">
-        <v>20</v>
-      </c>
-      <c r="AR75" t="s">
+      <c r="AL76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM76" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="76" spans="1:46" x14ac:dyDescent="0.3">
-      <c r="B76" t="s">
-        <v>108</v>
-      </c>
-      <c r="C76" t="s">
-        <v>185</v>
-      </c>
-      <c r="F76" t="s">
-        <v>109</v>
-      </c>
-      <c r="G76" t="s">
-        <v>187</v>
-      </c>
-      <c r="J76" t="s">
-        <v>110</v>
-      </c>
-      <c r="K76" t="s">
-        <v>186</v>
-      </c>
-      <c r="N76" t="s">
-        <v>109</v>
-      </c>
-      <c r="O76" t="s">
-        <v>187</v>
-      </c>
-      <c r="R76" t="s">
-        <v>124</v>
-      </c>
-      <c r="S76" t="s">
-        <v>183</v>
-      </c>
-      <c r="V76" t="s">
-        <v>111</v>
-      </c>
-      <c r="W76" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z76" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA76" t="s">
-        <v>186</v>
-      </c>
-      <c r="AD76" t="s">
-        <v>112</v>
-      </c>
-      <c r="AE76" t="s">
-        <v>184</v>
-      </c>
-      <c r="AH76" t="s">
-        <v>109</v>
-      </c>
-      <c r="AI76" t="s">
-        <v>187</v>
-      </c>
-      <c r="AL76" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM76" t="s">
-        <v>186</v>
-      </c>
       <c r="AP76" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="AQ76" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="77" spans="1:46" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="77" spans="1:46">
       <c r="B77" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F77" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J77" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="N77" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="R77" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="V77" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="Z77" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AD77" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="AH77" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AL77" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AP77" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="B92" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="1:23" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="A96" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23">
+      <c r="B92" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B96" s="14"/>
-      <c r="C96" s="14"/>
-      <c r="D96" s="14"/>
-      <c r="E96" s="14"/>
-      <c r="F96" s="14"/>
-      <c r="H96" s="14" t="s">
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14"/>
+    </row>
+    <row r="93" spans="1:23"/>
+    <row r="96" spans="1:23" ht="19.899999999999999">
+      <c r="A96" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="I96" s="14"/>
-      <c r="J96" s="14"/>
-      <c r="K96" s="14"/>
-      <c r="L96" s="14"/>
-      <c r="M96" s="14"/>
-      <c r="N96" s="14"/>
-      <c r="O96" s="14"/>
-      <c r="P96" s="14"/>
-      <c r="R96" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="S96" s="14"/>
-      <c r="U96" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="V96" s="14"/>
-      <c r="W96" s="14"/>
-    </row>
-    <row r="97" spans="1:23" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="B97" s="15"/>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="15"/>
-      <c r="H97" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="I97" s="15"/>
-      <c r="J97" s="15"/>
-      <c r="K97" s="15"/>
-      <c r="L97" s="15"/>
-      <c r="M97" s="15"/>
-      <c r="N97" s="15"/>
-      <c r="O97" s="15"/>
-      <c r="P97" s="15"/>
-      <c r="R97" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="S97" s="15"/>
-      <c r="U97" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="V97" s="15"/>
-      <c r="W97" s="15"/>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A99" s="16" t="s">
+      <c r="B96" s="15"/>
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="15"/>
+      <c r="F96" s="15"/>
+      <c r="H96" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="I96" s="15"/>
+      <c r="J96" s="15"/>
+      <c r="K96" s="15"/>
+      <c r="L96" s="15"/>
+      <c r="M96" s="15"/>
+      <c r="N96" s="15"/>
+      <c r="O96" s="15"/>
+      <c r="P96" s="15"/>
+      <c r="R96" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="S96" s="15"/>
+      <c r="U96" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="V96" s="15"/>
+      <c r="W96" s="15"/>
+    </row>
+    <row r="97" spans="1:23" ht="34.15" customHeight="1">
+      <c r="A97" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B97" s="13"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="H97" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="I97" s="13"/>
+      <c r="J97" s="13"/>
+      <c r="K97" s="13"/>
+      <c r="L97" s="13"/>
+      <c r="M97" s="13"/>
+      <c r="N97" s="13"/>
+      <c r="O97" s="13"/>
+      <c r="P97" s="13"/>
+      <c r="R97" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="S97" s="13"/>
+      <c r="U97" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="V97" s="13"/>
+      <c r="W97" s="13"/>
+    </row>
+    <row r="99" spans="1:23">
+      <c r="A99" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B99" t="s">
         <v>1</v>
       </c>
       <c r="C99" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D99" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="E99" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F99" t="s">
-        <v>107</v>
-      </c>
-      <c r="H99" s="16" t="s">
-        <v>114</v>
+        <v>7</v>
+      </c>
+      <c r="H99" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="I99" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="J99" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="K99" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="L99" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="M99" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="N99" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="O99" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="P99" t="s">
-        <v>204</v>
-      </c>
-      <c r="R99" s="16" t="s">
-        <v>104</v>
+        <v>211</v>
+      </c>
+      <c r="R99" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="S99" t="s">
-        <v>206</v>
-      </c>
-      <c r="U99" s="16" t="s">
-        <v>107</v>
+        <v>212</v>
+      </c>
+      <c r="U99" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="V99" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="W99" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A100" s="16">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23">
+      <c r="A100" s="12">
         <v>102</v>
       </c>
       <c r="B100" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C100" s="1">
         <v>46095</v>
       </c>
       <c r="D100" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="E100">
         <v>7</v>
       </c>
       <c r="F100" t="s">
-        <v>108</v>
-      </c>
-      <c r="H100" s="16" t="s">
-        <v>116</v>
+        <v>21</v>
+      </c>
+      <c r="H100" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="I100" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J100" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K100" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L100" t="s">
-        <v>216</v>
-      </c>
-      <c r="M100" s="10">
+        <v>217</v>
+      </c>
+      <c r="M100" s="9">
         <v>90026</v>
       </c>
       <c r="N100" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O100" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P100" t="s">
-        <v>219</v>
-      </c>
-      <c r="R100" s="16">
+        <v>220</v>
+      </c>
+      <c r="R100" s="12">
         <v>7</v>
       </c>
       <c r="S100" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="16" t="s">
-        <v>108</v>
+        <v>19</v>
+      </c>
+      <c r="U100" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="V100" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="W100" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A101" s="16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23">
+      <c r="A101" s="12">
         <v>103</v>
       </c>
       <c r="B101" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C101" s="1">
         <v>46194</v>
       </c>
       <c r="D101" t="s">
-        <v>115</v>
+        <v>38</v>
       </c>
       <c r="E101">
         <v>7</v>
       </c>
       <c r="F101" t="s">
-        <v>109</v>
-      </c>
-      <c r="H101" s="16" t="s">
-        <v>115</v>
+        <v>33</v>
+      </c>
+      <c r="H101" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="I101" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="J101" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K101" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L101" t="s">
-        <v>222</v>
-      </c>
-      <c r="M101" s="10">
+        <v>223</v>
+      </c>
+      <c r="M101" s="9">
         <v>78741</v>
       </c>
       <c r="N101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O101" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P101" t="s">
-        <v>225</v>
-      </c>
-      <c r="R101" s="16">
+        <v>226</v>
+      </c>
+      <c r="R101" s="12">
         <v>2</v>
       </c>
       <c r="S101" t="s">
-        <v>12</v>
-      </c>
-      <c r="U101" s="16" t="s">
-        <v>109</v>
+        <v>44</v>
+      </c>
+      <c r="U101" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="V101" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="W101" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A102" s="16">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23">
+      <c r="A102" s="12">
         <v>104</v>
       </c>
       <c r="B102" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C102" s="1">
         <v>46115</v>
       </c>
       <c r="D102" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="E102">
         <v>2</v>
       </c>
       <c r="F102" t="s">
-        <v>110</v>
-      </c>
-      <c r="H102" s="16" t="s">
-        <v>117</v>
+        <v>46</v>
+      </c>
+      <c r="H102" s="12" t="s">
+        <v>50</v>
       </c>
       <c r="I102" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="J102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K102" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L102" t="s">
-        <v>216</v>
-      </c>
-      <c r="M102" s="10">
+        <v>217</v>
+      </c>
+      <c r="M102" s="9">
         <v>90046</v>
       </c>
       <c r="N102" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O102" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P102" t="s">
-        <v>230</v>
-      </c>
-      <c r="R102" s="16">
+        <v>231</v>
+      </c>
+      <c r="R102" s="12">
         <v>3</v>
       </c>
       <c r="S102" t="s">
-        <v>16</v>
-      </c>
-      <c r="U102" s="16" t="s">
-        <v>110</v>
+        <v>56</v>
+      </c>
+      <c r="U102" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="V102" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="W102" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A103" s="16">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23">
+      <c r="A103" s="12">
         <v>105</v>
       </c>
       <c r="B103" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="C103" s="1">
         <v>46157</v>
       </c>
       <c r="D103" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="E103">
         <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>109</v>
-      </c>
-      <c r="H103" s="16" t="s">
-        <v>118</v>
+        <v>33</v>
+      </c>
+      <c r="H103" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="I103" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="J103" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K103" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L103" t="s">
-        <v>233</v>
-      </c>
-      <c r="M103" s="10">
+        <v>234</v>
+      </c>
+      <c r="M103" s="9">
         <v>60616</v>
       </c>
       <c r="N103" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O103" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P103" t="s">
-        <v>236</v>
-      </c>
-      <c r="R103" s="16">
+        <v>237</v>
+      </c>
+      <c r="R103" s="12">
         <v>6</v>
       </c>
       <c r="S103" t="s">
-        <v>19</v>
-      </c>
-      <c r="U103" s="16" t="s">
-        <v>124</v>
+        <v>66</v>
+      </c>
+      <c r="U103" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="V103" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="W103" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A104" s="16">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23">
+      <c r="A104" s="12">
         <v>106</v>
       </c>
       <c r="B104" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C104" s="1">
         <v>46109</v>
       </c>
       <c r="D104" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="E104">
         <v>6</v>
       </c>
       <c r="F104" t="s">
-        <v>124</v>
-      </c>
-      <c r="H104" s="16" t="s">
-        <v>119</v>
+        <v>68</v>
+      </c>
+      <c r="H104" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="I104" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="J104" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K104" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L104" t="s">
-        <v>239</v>
-      </c>
-      <c r="M104" s="10">
+        <v>240</v>
+      </c>
+      <c r="M104" s="9">
         <v>10011</v>
       </c>
       <c r="N104" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O104" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P104" t="s">
-        <v>242</v>
-      </c>
-      <c r="R104" s="16">
+        <v>243</v>
+      </c>
+      <c r="R104" s="12">
         <v>4</v>
       </c>
       <c r="S104" t="s">
-        <v>22</v>
-      </c>
-      <c r="U104" s="16" t="s">
-        <v>111</v>
+        <v>78</v>
+      </c>
+      <c r="U104" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="V104" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="W104" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A105" s="16">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23">
+      <c r="A105" s="12">
         <v>107</v>
       </c>
       <c r="B105" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="C105" s="1">
         <v>46130</v>
       </c>
       <c r="D105" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="E105">
         <v>4</v>
       </c>
       <c r="F105" t="s">
-        <v>111</v>
-      </c>
-      <c r="H105" s="16" t="s">
-        <v>120</v>
+        <v>80</v>
+      </c>
+      <c r="H105" s="12" t="s">
+        <v>88</v>
       </c>
       <c r="I105" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="J105" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K105" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L105" t="s">
-        <v>245</v>
-      </c>
-      <c r="M105" s="10">
+        <v>246</v>
+      </c>
+      <c r="M105" s="9">
         <v>97214</v>
       </c>
       <c r="N105" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O105" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P105" t="s">
-        <v>248</v>
-      </c>
-      <c r="R105" s="16">
+        <v>249</v>
+      </c>
+      <c r="R105" s="12">
         <v>5</v>
       </c>
       <c r="S105" t="s">
-        <v>26</v>
-      </c>
-      <c r="U105" s="16" t="s">
-        <v>112</v>
+        <v>84</v>
+      </c>
+      <c r="U105" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="V105" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="W105" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A106" s="16">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23">
+      <c r="A106" s="12">
         <v>108</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="C106" s="1">
         <v>46144</v>
       </c>
       <c r="D106" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="E106">
         <v>5</v>
       </c>
       <c r="F106" t="s">
-        <v>110</v>
-      </c>
-      <c r="H106" s="16" t="s">
-        <v>121</v>
+        <v>46</v>
+      </c>
+      <c r="H106" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="I106" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="J106" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K106" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L106" t="s">
-        <v>251</v>
-      </c>
-      <c r="M106" s="10">
+        <v>252</v>
+      </c>
+      <c r="M106" s="9">
         <v>48226</v>
       </c>
       <c r="N106" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O106" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P106" t="s">
-        <v>254</v>
-      </c>
-      <c r="R106" s="16">
+        <v>255</v>
+      </c>
+      <c r="R106" s="12">
         <v>1</v>
       </c>
       <c r="S106" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A107" s="16">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23">
+      <c r="A107" s="12">
         <v>109</v>
       </c>
       <c r="B107" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C107" s="1">
         <v>46181</v>
       </c>
       <c r="D107" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>112</v>
-      </c>
-      <c r="H107" s="16" t="s">
-        <v>122</v>
+        <v>95</v>
+      </c>
+      <c r="H107" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="J107" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K107" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L107" t="s">
-        <v>239</v>
-      </c>
-      <c r="M107" s="10">
+        <v>240</v>
+      </c>
+      <c r="M107" s="9">
         <v>10012</v>
       </c>
       <c r="N107" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O107" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P107" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A108" s="16">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23">
+      <c r="A108" s="12">
         <v>110</v>
       </c>
       <c r="B108" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="C108" s="1">
         <v>46215</v>
       </c>
       <c r="D108" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="E108">
         <v>7</v>
       </c>
       <c r="F108" t="s">
-        <v>109</v>
-      </c>
-      <c r="H108" s="16" t="s">
-        <v>123</v>
+        <v>33</v>
+      </c>
+      <c r="H108" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="I108" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="J108" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K108" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L108" t="s">
-        <v>261</v>
-      </c>
-      <c r="M108" s="10">
+        <v>262</v>
+      </c>
+      <c r="M108" s="9">
         <v>33132</v>
       </c>
       <c r="N108" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O108" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A109" s="16">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23">
+      <c r="A109" s="12">
         <v>111</v>
       </c>
       <c r="B109" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="C109" s="1">
         <v>46102</v>
       </c>
       <c r="D109" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E109">
         <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A110" s="16">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23">
+      <c r="A110" s="12">
         <v>112</v>
       </c>
       <c r="B110" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C110" s="1">
         <v>46137</v>
       </c>
       <c r="D110" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E110">
         <v>1</v>
       </c>
       <c r="F110" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="14"/>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D114" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="28.9">
+      <c r="A115" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="E115" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="F115" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="B114" s="11" t="s">
+    </row>
+    <row r="116" spans="1:6" ht="28.9">
+      <c r="A116" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="C114" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D114" s="11" t="s">
+      <c r="B116" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="E114" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="F114" s="11" t="s">
+      <c r="C116" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="E116" s="11" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A115" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="B115" s="12" t="s">
+      <c r="F116" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="28.9">
+      <c r="A117" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="C115" s="12" t="s">
+      <c r="B117" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="D115" s="12" t="s">
+      <c r="C117" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="E117" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="F117" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="43.15">
+      <c r="A118" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="B118" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="E115" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="F115" s="12" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="B116" s="12" t="s">
+      <c r="C118" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="E118" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="F118" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="28.9">
+      <c r="A119" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="B119" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="D116" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="E116" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="F116" s="12" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="B117" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="E117" s="12" t="s">
+      <c r="C119" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="F117" s="12" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A118" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="B118" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="D118" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="E118" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="F118" s="12" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A119" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="C119" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="D119" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="E119" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="F119" s="12" t="s">
-        <v>284</v>
+      <c r="D119" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="E119" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="F119" s="11" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -7435,6 +7437,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CA5D0A6329BB324E86983B32928CFC2E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d7eac4bce3bbb09c82bd908806be82e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xmlns:ns3="ced60a7f-99b1-48d2-b555-34851c8026ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eb51570e5b7cb8bd524bc2df5324d4a3" ns2:_="" ns3:_="">
     <xsd:import namespace="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
@@ -7675,49 +7686,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
-    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6414E68-BBC1-4A96-B078-EF7EE95D29CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
-    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6414E68-BBC1-4A96-B078-EF7EE95D29CE}"/>
 </file>